--- a/Script_5_single_factor_pathway/region_vs_region_GSEA/GSEA_summary_bottom_vs_top.xlsx
+++ b/Script_5_single_factor_pathway/region_vs_region_GSEA/GSEA_summary_bottom_vs_top.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Proteomics_Data_Analysis\Fei\UW madison rat region age and sex proteomics\paper analysis\final analysis\single factor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/outobi/Downloads/final analysis/final code/Script_5_single_factor_pathway/region_vs_region_GSEA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B044607-6F5E-4E93-BD91-DFB8975BDEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A4CD67-4674-5944-98A7-4C79798C69D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{660A23B4-67C1-4BCA-B8AE-ADAB9C846779}"/>
+    <workbookView xWindow="38220" yWindow="3000" windowWidth="23260" windowHeight="13900" activeTab="2" xr2:uid="{660A23B4-67C1-4BCA-B8AE-ADAB9C846779}"/>
   </bookViews>
   <sheets>
     <sheet name="Reactome" sheetId="1" r:id="rId1"/>
@@ -623,9 +623,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A04413EB-FBA2-4E25-A1EF-ACAA355DCF62}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -654,7 +654,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -684,7 +684,7 @@
         <v>2.440260903766192</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -710,11 +710,11 @@
         <v>5.2413E-3</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I8" si="0">-LOG10(H3)</f>
+        <f t="shared" ref="I3:I7" si="0">-LOG10(H3)</f>
         <v>2.2805609815651424</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -744,7 +744,7 @@
         <v>2.2641696447105106</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -774,7 +774,7 @@
         <v>2.1320495765801923</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -804,7 +804,7 @@
         <v>2.0645985496651682</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -842,9 +842,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CAE97F3-1A2C-4E94-A369-A841C47AC8D9}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -873,7 +884,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -903,7 +914,7 @@
         <v>15.657577319177793</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -933,7 +944,7 @@
         <v>15.657577319177793</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -963,7 +974,7 @@
         <v>15.657577319177793</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -993,7 +1004,7 @@
         <v>3.492616444263613</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1023,7 +1034,7 @@
         <v>3.4346244972859266</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1053,7 +1064,7 @@
         <v>3.4134464500971187</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1083,7 +1094,7 @@
         <v>3.3165296859254019</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1113,7 +1124,7 @@
         <v>3.1458336837935246</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1143,7 +1154,7 @@
         <v>3.0946845369166041</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1173,7 +1184,7 @@
         <v>2.961141498440234</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1203,7 +1214,7 @@
         <v>2.7558713813305333</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1233,7 +1244,7 @@
         <v>2.6797082807604395</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1263,7 +1274,7 @@
         <v>1.949504241116145</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1301,9 +1312,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D94077-B433-4F09-8663-2957B1BFC9ED}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="32.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1329,7 +1343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1355,7 +1369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1381,7 +1395,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -1407,7 +1421,7 @@
         <v>8.0531000000000005E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -1433,7 +1447,7 @@
         <v>6.4425000000000003E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -1459,7 +1473,7 @@
         <v>1.2563E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -1485,7 +1499,7 @@
         <v>1.3422E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -1519,9 +1533,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CE87FBA-1BFE-4B68-9BD8-A28B7C9D2659}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1547,7 +1561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1581,9 +1595,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72B7E0C-BED3-4DCE-B12B-C0E0A708B461}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1615,7 +1629,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -1648,7 +1662,7 @@
         <v>15.657577319177793</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>54</v>
       </c>
@@ -1681,7 +1695,7 @@
         <v>15.657577319177793</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -1714,7 +1728,7 @@
         <v>15.657577319177793</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1747,7 +1761,7 @@
         <v>3.492616444263613</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -1780,7 +1794,7 @@
         <v>3.4346244972859266</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -1813,7 +1827,7 @@
         <v>3.4134464500971187</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -1846,7 +1860,7 @@
         <v>3.3165296859254019</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -1879,7 +1893,7 @@
         <v>3.1458336837935246</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -1912,7 +1926,7 @@
         <v>3.0946845369166041</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -1945,7 +1959,7 @@
         <v>2.961141498440234</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -1978,7 +1992,7 @@
         <v>2.7558713813305333</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -2011,7 +2025,7 @@
         <v>2.6797082807604395</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -2044,7 +2058,7 @@
         <v>1.949504241116145</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -2077,7 +2091,7 @@
         <v>1.6619421245802439</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -2110,7 +2124,7 @@
         <v>15.657577319177793</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2143,7 +2157,7 @@
         <v>15.657577319177793</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -2176,7 +2190,7 @@
         <v>3.0940369079883445</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -2209,7 +2223,7 @@
         <v>2.1909455727770575</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -2242,7 +2256,7 @@
         <v>1.9009066402269004</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -2275,7 +2289,7 @@
         <v>1.8721827655197267</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -2308,7 +2322,7 @@
         <v>1.5241545478538367</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>56</v>
       </c>
